--- a/artfynd/A 4802-2026 artfynd.xlsx
+++ b/artfynd/A 4802-2026 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>105933861</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97983</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>538867.6111680623</v>
+        <v>538867</v>
       </c>
       <c r="R2" t="n">
-        <v>7246020.496166046</v>
+        <v>7246020</v>
       </c>
       <c r="S2" t="n">
         <v>50</v>
@@ -752,19 +747,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,12 +780,7 @@
         <v>105933637</v>
       </c>
       <c r="B3" t="n">
-        <v>78448</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80357</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,10 +815,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>538867.6111680623</v>
+        <v>538867</v>
       </c>
       <c r="R3" t="n">
-        <v>7246020.496166046</v>
+        <v>7246020</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -868,19 +848,9 @@
           <t>2022-11-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-11-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
